--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_570_Niue_New_Zealand.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_570_Niue_New_Zealand.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2802479775fb424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R67674d3f8e774d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re57d162f83f34d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4efd2be90cf84381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2fe4df74bfbf47b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfe682443174844eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R861243613b924712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd667f5157c6040ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R54cc7c46bd874c61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R429002ba700b4659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf65363618f3744f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R61bd96b1dbf24155"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ570CommercialTable" displayName="EEZ570CommercialTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ570CommercialTable" displayName="EEZ570CommercialTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ570FunctionalTable" displayName="EEZ570FunctionalTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ570FunctionalTable" displayName="EEZ570FunctionalTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ570ValidationTable" displayName="EEZ570ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ570ValidationTable" displayName="EEZ570ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5384,7 +5338,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49ed862489e44cd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf2bb8b68d8f4766"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5394,20 +5348,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5415,390 +5359,136 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4.0228625055</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.8967064739960944</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>78.83271319688971</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4.0228625055</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>108.7857438054178</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$71,A2,'Species'!$U$2:$U$71))</x:f>
-        <x:v>437.63008988774413</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.8967064739960944</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>78.83271319688971</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>317.13316612660265</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>120.49692376114149</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.3799568655428425</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.37995686554284247</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>23.9955783633</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.133269230805496</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>13.591557626090674</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>23.9955783633</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>22.337364883979767</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$71,A3,'Species'!$U$2:$U$71))</x:f>
-        <x:v>535.9979895031621</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.133269230805496</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>13.591557626090674</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>326.1372860961665</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>209.86070340699558</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.6434735074882392</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.6434735074882391</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>103.50983931919998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3006942307137535</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>199.84543428336306</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>103.50983931919998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>202.97550424590048</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$71,A4,'Species'!$U$2:$U$71))</x:f>
-        <x:v>21009.96183022675</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3006942307137535</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>199.84543428336306</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20685.96879134665</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>323.99303888010036</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0156624542049795</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.015662454204979418</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>54.4941974648</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5642146415689733</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>366.61872402624675</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>54.4941974648</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1093.9520800509358</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$71,A5,'Species'!$U$2:$U$71))</x:f>
-        <x:v>59614.04066732439</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5642146415689733</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>366.61872402624675</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>19978.593141379308</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>39635.447525945085</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.9838958251696335</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.9838958251696337</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>152.83627933860004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.367133239185007</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2328.8056129753945</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>152.83627933860004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2356.699865080186</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$71,A6,'Species'!$U$2:$U$71))</x:f>
-        <x:v>360189.23889663635</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.367133239185007</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2328.8056129753945</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>355925.9851900071</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4263.253706629272</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0119779220512752</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0119779220512753</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>610.6685847154</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.349470066562178</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2235.991079318828</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>610.6685847154</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2270.7381885564027</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$71,A7,'Species'!$U$2:$U$71))</x:f>
-        <x:v>1386668.4758649496</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.349470066562178</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2235.991079318828</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1365449.5078438884</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>21218.96802106127</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.015539914071643</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.015539914071643016</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b5b7506699f40e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a9fc54ce5c14ece"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5808,20 +5498,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5829,714 +5509,250 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.36157720860000003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.36157720860000003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$71,A2,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>228.1397953628168</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>228.1397953628168</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.9221104445000003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.470990312166484</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2957.946482722862</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.9221104445000003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2962.7520855064936</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$71,A3,'Species'!$U$2:$U$71))</x:f>
-        <x:v>8657.488813522683</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.470990312166484</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2957.946482722862</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8643.446311436515</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>14.042502086167588</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0016246415584935</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0016246415584935548</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>615.4591426236</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.349642540265068</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2236.8792468292404</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>615.4591426236</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2271.3890192090525</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$71,A4,'Species'!$U$2:$U$71))</x:f>
-        <x:v>1397947.138327063</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.349642540265068</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2236.8792468292404</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1376707.7834060483</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>21239.354921014747</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0154276420726462</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.015427642072646275</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1.6859539272000001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1.6859539272000001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$71,A5,'Species'!$U$2:$U$71))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5210.095720654514</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>5210.095720654514</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>152.83627933860004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.367133239185007</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2328.8056129753945</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>152.83627933860004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2356.699865080186</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$71,A6,'Species'!$U$2:$U$71))</x:f>
-        <x:v>360189.23889663635</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.367133239185007</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2328.8056129753945</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>355925.9851900071</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4263.253706629272</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0119779220512752</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0119779220512753</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4.0228625055</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.8967064739960944</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>78.83271319688971</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4.0228625055</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>108.7857438054178</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$71,A7,'Species'!$U$2:$U$71))</x:f>
-        <x:v>437.63008988774413</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.8967064739960944</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>78.83271319688971</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>317.13316612660265</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>120.49692376114149</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3799568655428425</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.37995686554284247</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>84.09783062099999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.267753800672465</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>185.24811635660512</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>84.09783062099999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>188.4768355394754</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$71,A8,'Species'!$U$2:$U$71))</x:f>
-        <x:v>15850.492991180872</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.267753800672465</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>185.24811635660512</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>15578.964712217075</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>271.52827896379677</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0174291606650128</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01742916066501283</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>25.3008690798</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8845261681644536</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>766.5247252780109</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>25.3008690798</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1057.6390399474067</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$71,A9,'Species'!$U$2:$U$71))</x:f>
-        <x:v>26759.1868833947</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8845261681644536</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>766.5247252780109</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>19393.741720688617</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7365.445162706084</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3797846371671985</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3797846371671984</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>20.989624764199995</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.7444292143974667</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>55.51741219851268</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>20.989624764199995</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>283.6888398594144</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$71,A10,'Species'!$U$2:$U$71))</x:f>
-        <x:v>5954.522298440331</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.7444292143974667</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>55.51741219851268</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1165.2896499262006</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4789.23264851413</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>5.109907479927792</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>4.109907479927792</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>24.2838287262</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.1337062682715637</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>13.605241911578203</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>24.2838287262</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>22.275602916470064</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$71,A11,'Species'!$U$2:$U$71))</x:f>
-        <x:v>540.9369259964002</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.1337062682715637</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>13.605241911578203</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>330.38736435928297</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>210.54956163711722</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.637280914315334</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.637280914315334</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.009436309</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5699999999999994</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>371.535229097172</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.009436309</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$71,A12,'Species'!$U$2:$U$71))</x:f>
-        <x:v>3.50592122614671</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5699999999999994</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>371.535229097172</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3.5059212261467065</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>3.552713678800501e-15</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.0133466925339971e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>17.557826158599998</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5070118236701355</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>321.3748031760682</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>17.557826158599998</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>380.2844734222337</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$71,A13,'Species'!$U$2:$U$71))</x:f>
-        <x:v>6676.96867516232</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5070118236701355</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>321.3748031760682</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5642.642925919696</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1034.3257492426246</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1833051927655054</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.1833051927655053</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bae82a417c442d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8743e270e1ae40de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6711,7 +5927,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6810,7 +6026,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1828455.3453385283</x:v>
+        <x:v>1762683.3254188441</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6824,7 +6040,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1828455.3453385283</x:v>
+        <x:v>1789147.115883973</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6838,7 +6054,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-65772.01991968439</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6852,7 +6068,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-39308.22945455555</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6863,9 +6079,9 @@
         <x:v>EEZ_570</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6877,47 +6093,19 @@
         <x:v>EEZ_570</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_570</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_570</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03e4d726650e43ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c83534249e47ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6964,7 +6152,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
